--- a/experiment_results/wedos_grid/rtt_bursts_S3_atk10pct_wu400000_stage1a_rep1.xlsx
+++ b/experiment_results/wedos_grid/rtt_bursts_S3_atk10pct_wu400000_stage1a_rep1.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -605,12 +605,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>662731</t>
+          <t>359041</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>718054</t>
+          <t>359041</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>749881</t>
+          <t>390868</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -776,12 +776,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>853124</t>
+          <t>462285</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>972784</t>
+          <t>510527</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1084192</t>
+          <t>573694</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1167143</t>
+          <t>593478</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1244367</t>
+          <t>650918</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1061,12 +1061,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1328170</t>
+          <t>677281</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1404248</t>
+          <t>726996</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1486667</t>
+          <t>759700</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1558018</t>
+          <t>798346</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1628108</t>
+          <t>829791</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1665195</t>
+          <t>835433</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1670837</t>
+          <t>835433</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
